--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_41_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_41_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>8</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
         <v>10</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>4</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
@@ -3099,10 +3099,10 @@
         <v>28</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>106</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X30" t="n">
         <v>36</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>1</v>
@@ -5076,16 +5076,16 @@
         <v>12</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>8</v>
@@ -5272,16 +5272,16 @@
         <v>16</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>3</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6056,16 +6056,16 @@
         <v>18</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X44" t="n">
         <v>8</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>88</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X48" t="n">
         <v>27</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_41_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_41_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="P2" t="n">
         <v>6</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2131,10 +2131,10 @@
         <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3839,14 +3839,14 @@
         <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -5088,10 +5088,10 @@
         <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6068,14 +6068,14 @@
         <v>3</v>
       </c>
       <c r="X44" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y44" t="n">
         <v>8</v>
       </c>
-      <c r="Y44" t="n">
-        <v>12</v>
-      </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6460,14 +6460,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>7</v>
       </c>
       <c r="X48" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Y48" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="AA48" t="n">
